--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigS6_d1_d4_redundancy_audit_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigS6_d1_d4_redundancy_audit_source_data.xlsx
@@ -584,82 +584,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42357</v>
+        <v>42189</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2227504168044645</v>
+        <v>0.1675457363229493</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0842835894893406</v>
+        <v>0.08592287089051648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.408621951507425</v>
+        <v>0.2648794709521439</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05040489175342919</v>
+        <v>0.03723719452937969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03444012481718505</v>
+        <v>0.02275920458416937</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01596476693624414</v>
+        <v>0.01447798994521032</v>
       </c>
       <c r="I2" t="n">
-        <v>1.463551366929947</v>
+        <v>1.63613778292062</v>
       </c>
       <c r="J2" t="n">
-        <v>0.113909192765299</v>
+        <v>0.1187542520220727</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1169007038242681</v>
+        <v>0.1170736164042219</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5980392156862745</v>
+        <v>0.4333793103448276</v>
       </c>
       <c r="M2" t="n">
-        <v>0.123353362606887</v>
+        <v>0.1405816554809843</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1668313790378424</v>
+        <v>0.113725304394172</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005422533206898865</v>
+        <v>0.006746926888034772</v>
       </c>
       <c r="P2" t="n">
-        <v>1.160470853475703</v>
+        <v>1.309743199189141</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0783227060951696</v>
+        <v>0.08265892192112832</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04099942418428937</v>
+        <v>0.0565452660734771</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4658745340298883</v>
+        <v>0.3337773683330197</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08549616658230705</v>
+        <v>0.09546616194060994</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2821722328424635</v>
+        <v>0.2204064735842722</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02642647407576601</v>
+        <v>0.02291970917587486</v>
       </c>
       <c r="W2" t="n">
-        <v>1.721523251049269</v>
+        <v>2.002008742772535</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1491222635974869</v>
+        <v>0.1563471527248994</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1831459672322981</v>
+        <v>0.1757950768229494</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.7103427882375025</v>
+        <v>0.5134803118424246</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1606468838526501</v>
+        <v>0.1870217414837866</v>
       </c>
       <c r="AB2" t="n">
         <v>37</v>
@@ -677,82 +677,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6042</v>
+        <v>6027</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1765264105735845</v>
+        <v>0.1904147099772479</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006620324395895399</v>
+        <v>0.008627841380454622</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2909632571996028</v>
+        <v>0.2254853160776506</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004468718967229395</v>
+        <v>0.006304961008793761</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001926271149947718</v>
+        <v>0.001945451540739643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002542447817281677</v>
+        <v>0.004359509468054118</v>
       </c>
       <c r="I3" t="n">
-        <v>2.319880546075086</v>
+        <v>3.240872813720495</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01524562394127612</v>
+        <v>0.02767662053896577</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06902419211315183</v>
+        <v>0.1127961378096023</v>
       </c>
       <c r="L3" t="n">
-        <v>0.675</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01535836177474403</v>
+        <v>0.0279617365710081</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06706436721936604</v>
+        <v>0.08522238028286595</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002050444641217677</v>
+        <v>0.0005472444073670868</v>
       </c>
       <c r="P3" t="n">
-        <v>1.209267929475772</v>
+        <v>1.648618873739</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004996342025921977</v>
+        <v>0.00710816641330591</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00756148811157931</v>
+        <v>0.02048391943007471</v>
       </c>
       <c r="S3" t="n">
-        <v>0.279896551724138</v>
+        <v>0.3076086956521739</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005047186066855764</v>
+        <v>0.00721030102954342</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2703918771750108</v>
+        <v>0.2845317570385227</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00573328505346999</v>
+        <v>0.008907636865898348</v>
       </c>
       <c r="W3" t="n">
-        <v>3.152230557803959</v>
+        <v>4.564864182846164</v>
       </c>
       <c r="X3" t="n">
-        <v>0.029401476664144</v>
+        <v>0.05179325627646379</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1208207171626915</v>
+        <v>0.1832335464446334</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.875</v>
+        <v>0.9029588534442904</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02968892344666714</v>
+        <v>0.05200482868095324</v>
       </c>
       <c r="AB3" t="n">
         <v>37</v>
@@ -770,82 +770,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6043</v>
+        <v>6027</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1737843240939324</v>
+        <v>0.1631600098281813</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04285950686744994</v>
+        <v>0.04496432719429235</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2490484858513983</v>
+        <v>0.1939605110336818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0134039384411716</v>
+        <v>0.01426912228305957</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01067409528967602</v>
+        <v>0.008721303880890619</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002729843151495588</v>
+        <v>0.005547818402168947</v>
       </c>
       <c r="I4" t="n">
-        <v>1.25574468630947</v>
+        <v>1.636122588770798</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0481283422459893</v>
+        <v>0.06351550960118169</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03116580600942521</v>
+        <v>0.06770855896368783</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3127413127413127</v>
+        <v>0.3173431734317343</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05382059800664452</v>
+        <v>0.07356715141146279</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.001982098043090584</v>
+        <v>-0.03387605541047234</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01031371593778651</v>
+        <v>-0.006080641563356101</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3689055877910373</v>
+        <v>0.5599153515776873</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0152309675708959</v>
+        <v>0.02501627374508731</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.09010988781819848</v>
+        <v>-0.05707116452344969</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07645820751298467</v>
+        <v>0.08847702589807853</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01738934722389498</v>
+        <v>0.02954064578879941</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3206500907184227</v>
+        <v>0.3162551331795641</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01573390030332443</v>
+        <v>0.01809019327608259</v>
       </c>
       <c r="W4" t="n">
-        <v>3.180154576586025</v>
+        <v>3.983244589637298</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08870324704977527</v>
+        <v>0.112578151681428</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1984472589185274</v>
+        <v>0.238026928879516</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8197101291933557</v>
+        <v>0.7973041474654378</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09779716187196499</v>
+        <v>0.1243873520672259</v>
       </c>
       <c r="AB4" t="n">
         <v>37</v>
@@ -863,82 +863,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6043</v>
+        <v>6027</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.01186272519085512</v>
+        <v>0.08671502564648467</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1629985106735065</v>
+        <v>0.1664177866268459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3653814330630482</v>
+        <v>0.2475526796084287</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05328479232169452</v>
+        <v>0.05276256844201095</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05955662941702837</v>
+        <v>0.04119716901397943</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.006271837095333847</v>
+        <v>0.01156539942803152</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8946912013536379</v>
+        <v>1.280732868418872</v>
       </c>
       <c r="J5" t="n">
-        <v>0.112156043190526</v>
+        <v>0.1460725769407441</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03526226553989256</v>
+        <v>0.07194732974529185</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3269035532994924</v>
+        <v>0.317048853439681</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.2131367292225201</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1774989790344486</v>
+        <v>-0.02680055228100146</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.02948247600225741</v>
+        <v>-0.003318860299304117</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6103781807254661</v>
+        <v>0.9414352039888385</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07704150550874417</v>
+        <v>0.09289484874994955</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1466801654475055</v>
+        <v>-0.01922667741084759</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2042208707914684</v>
+        <v>0.2164961779913548</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09562838279100143</v>
+        <v>0.1224512401191431</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1615365851357478</v>
+        <v>0.1876280074963174</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01476717975059783</v>
+        <v>0.02567775598946356</v>
       </c>
       <c r="W5" t="n">
-        <v>1.343199216861219</v>
+        <v>1.832989778502581</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1473225612495705</v>
+        <v>0.1952026395039858</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09938784781586645</v>
+        <v>0.1735425981451426</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5611647727272725</v>
+        <v>0.472959496505327</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1936003118503118</v>
+        <v>0.3021521124232521</v>
       </c>
       <c r="AB5" t="n">
         <v>37</v>
@@ -956,82 +956,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6043</v>
+        <v>6027</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.06167772987111848</v>
+        <v>-0.04564806481978207</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03888796955154725</v>
+        <v>0.04114816658370665</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4575541949362899</v>
+        <v>0.3641944582711133</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03028297203375807</v>
+        <v>0.02887008461921354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01779335360086515</v>
+        <v>0.01498593423780257</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01248961843289291</v>
+        <v>0.01388415038141097</v>
       </c>
       <c r="I6" t="n">
-        <v>1.701926051325459</v>
+        <v>1.926478800793593</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06496272630457935</v>
+        <v>0.07668576465403261</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1296746491509609</v>
+        <v>0.1452578098533057</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7787234042553192</v>
+        <v>0.7016129032258065</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06618444846292948</v>
+        <v>0.07927107061503418</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1959889070982148</v>
+        <v>-0.180309506972047</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002202767626492414</v>
+        <v>0.00277790770252931</v>
       </c>
       <c r="P6" t="n">
-        <v>1.158188050495382</v>
+        <v>1.296290561485606</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02606740661959932</v>
+        <v>0.03043012037736057</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02617786548177888</v>
+        <v>0.04143486425805922</v>
       </c>
       <c r="S6" t="n">
-        <v>0.532884056732741</v>
+        <v>0.4204342532467533</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02647834805109753</v>
+        <v>0.0311686132659287</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08596585399519888</v>
+        <v>0.1011538082600346</v>
       </c>
       <c r="V6" t="n">
-        <v>0.023812595720632</v>
+        <v>0.02581248218768323</v>
       </c>
       <c r="W6" t="n">
-        <v>2.136047087493572</v>
+        <v>2.602975464407654</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1053011435816693</v>
+        <v>0.1271726406064055</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2121835425744915</v>
+        <v>0.2394375360120907</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9357391500904159</v>
+        <v>0.8917531351809703</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1077917649963938</v>
+        <v>0.1319508730007329</v>
       </c>
       <c r="AB6" t="n">
         <v>37</v>
@@ -1049,82 +1049,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6062</v>
+        <v>6027</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1186307474112222</v>
+        <v>0.0610963723696231</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09848234905971627</v>
+        <v>0.09905425584868094</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2522269877928077</v>
+        <v>0.09407665505226481</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03942593203563181</v>
+        <v>0.01675792268126763</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02483990625409208</v>
+        <v>0.009318693058935141</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01458602578153973</v>
+        <v>0.00743922962233249</v>
       </c>
       <c r="I7" t="n">
-        <v>1.587201321628855</v>
+        <v>1.798312550406353</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1266560678325384</v>
+        <v>0.09501411100658513</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1127171475801546</v>
+        <v>0.08530125401929176</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4003350083752094</v>
+        <v>0.169179229480737</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1563113145846959</v>
+        <v>0.1781305114638448</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01156811041045357</v>
+        <v>-0.06001727262062576</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006045911893468744</v>
+        <v>0.003385622312404963</v>
       </c>
       <c r="P7" t="n">
-        <v>1.267034389262091</v>
+        <v>1.413106406916138</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08676131270338307</v>
+        <v>0.06184141586920007</v>
       </c>
       <c r="R7" t="n">
-        <v>0.05190237356027871</v>
+        <v>0.0452049795593497</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2733565080275229</v>
+        <v>0.09593275150003897</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1091052456996636</v>
+        <v>0.1301093651413635</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2097728604212657</v>
+        <v>0.1638741790298856</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02175283855003024</v>
+        <v>0.0110336851327775</v>
       </c>
       <c r="W7" t="n">
-        <v>1.914010489202533</v>
+        <v>2.285025215555617</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1587691625638985</v>
+        <v>0.1165782487500553</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1597914908383725</v>
+        <v>0.1199925075537106</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4977184087363494</v>
+        <v>0.2500103648424544</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2039924071938699</v>
+        <v>0.2270253000043322</v>
       </c>
       <c r="AB7" t="n">
         <v>37</v>
@@ -1142,82 +1142,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6062</v>
+        <v>6027</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4662385609145733</v>
+        <v>0.3919686589617536</v>
       </c>
       <c r="D8" t="n">
-        <v>0.22154404486968</v>
+        <v>0.2228305956528953</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5369515011547344</v>
+        <v>0.2769205243072839</v>
       </c>
       <c r="F8" t="n">
-        <v>0.196799736060706</v>
+        <v>0.1317405010784802</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1189584074646665</v>
+        <v>0.06170636537990414</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07784132859603952</v>
+        <v>0.07003413569857603</v>
       </c>
       <c r="I8" t="n">
-        <v>1.654357520876868</v>
+        <v>2.134958043103021</v>
       </c>
       <c r="J8" t="n">
-        <v>0.350367107195301</v>
+        <v>0.3579801623083859</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3759087251405212</v>
+        <v>0.376091852749909</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8883097542814594</v>
+        <v>0.5912137006701415</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3665130568356375</v>
+        <v>0.475733972438586</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3203615074518942</v>
+        <v>0.218614467898753</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04147687644860795</v>
+        <v>0.02783770247284411</v>
       </c>
       <c r="P8" t="n">
-        <v>1.402141044349512</v>
+        <v>1.640574490653127</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2011422649643509</v>
+        <v>0.2000885953856442</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2468062646766891</v>
+        <v>0.2065825474876584</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7799786332612312</v>
+        <v>0.3921726355088496</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2095692037956682</v>
+        <v>0.259234986721494</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5683761281914336</v>
+        <v>0.5186186436670105</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1109448197307778</v>
+        <v>0.1068973183214334</v>
       </c>
       <c r="W8" t="n">
-        <v>1.998736645407601</v>
+        <v>2.852140024421854</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4899731599111564</v>
+        <v>0.4892522981312848</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4938308988223415</v>
+        <v>0.5178076256527341</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9520174151326396</v>
+        <v>0.726337625575845</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5183927679990016</v>
+        <v>0.6557729250472045</v>
       </c>
       <c r="AB8" t="n">
         <v>37</v>
@@ -1235,82 +1235,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6062</v>
+        <v>6027</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0189357999099188</v>
+        <v>0.0448706116406331</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01831078851864071</v>
+        <v>0.01841712294673967</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7073573078192016</v>
+        <v>0.4519661523145844</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01484658528538436</v>
+        <v>0.009955201592832254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01295227007059244</v>
+        <v>0.008323916194942568</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001894315214791921</v>
+        <v>0.001631285397889686</v>
       </c>
       <c r="I9" t="n">
-        <v>1.146253529649052</v>
+        <v>1.195975711394214</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02088651659317707</v>
+        <v>0.02162162162162162</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03105442203879386</v>
+        <v>0.02437804762344486</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02098880597014926</v>
+        <v>0.02202643171806168</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0672374869360992</v>
+        <v>-0.03517842998222252</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001881155782700342</v>
+        <v>-0.0006505187753616267</v>
       </c>
       <c r="P9" t="n">
-        <v>1.026165042853888</v>
+        <v>0.8664534927853473</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002483273126026423</v>
+        <v>0.002737328130568916</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005687249643047997</v>
+        <v>-0.01054954707243298</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7702442827442828</v>
+        <v>0.4309729064039409</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002483875702979208</v>
+        <v>0.002741734887225746</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1014178155821162</v>
+        <v>0.1170212720774084</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004652806573393717</v>
+        <v>0.004637425377774331</v>
       </c>
       <c r="W9" t="n">
-        <v>1.446180531773299</v>
+        <v>1.852986650277651</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04667585432457952</v>
+        <v>0.04725958265869396</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.05626452243109414</v>
+        <v>0.05603554008411353</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04722071142936538</v>
+        <v>0.04917890064458474</v>
       </c>
       <c r="AB9" t="n">
         <v>37</v>
@@ -1384,25 +1384,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6042</v>
+        <v>6027</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>1642</v>
+        <v>1283</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008526187576126675</v>
+        <v>0.01870615744349182</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008526187576126675</v>
+        <v>0.01870615744349182</v>
       </c>
     </row>
     <row r="3">
@@ -1412,25 +1412,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6043</v>
+        <v>6027</v>
       </c>
       <c r="C3" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D3" t="n">
-        <v>1384</v>
+        <v>1062</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0254071661237785</v>
+        <v>0.0361544782251438</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2052631578947368</v>
+        <v>0.221105527638191</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02817919075144509</v>
+        <v>0.04143126177024482</v>
       </c>
     </row>
     <row r="4">
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6043</v>
+        <v>6027</v>
       </c>
       <c r="C4" t="n">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="D4" t="n">
-        <v>2080</v>
+        <v>1383</v>
       </c>
       <c r="E4" t="n">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05104761904761905</v>
+        <v>0.09473684210526316</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1973490427098674</v>
+        <v>0.2582496413199426</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06442307692307692</v>
+        <v>0.1301518438177874</v>
       </c>
     </row>
     <row r="5">
@@ -1468,25 +1468,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6043</v>
+        <v>6027</v>
       </c>
       <c r="C5" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D5" t="n">
-        <v>2720</v>
+        <v>2162</v>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03605243991260015</v>
+        <v>0.04219600725952813</v>
       </c>
       <c r="G5" t="n">
-        <v>0.792</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03639705882352941</v>
+        <v>0.04301572617946346</v>
       </c>
     </row>
     <row r="6">
@@ -1496,25 +1496,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6062</v>
+        <v>6027</v>
       </c>
       <c r="C6" t="n">
         <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>1445</v>
+        <v>497</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04107744107744108</v>
+        <v>0.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6039603960396039</v>
+        <v>0.2277227722772277</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04221453287197232</v>
+        <v>0.04627766599597585</v>
       </c>
     </row>
     <row r="7">
@@ -1524,25 +1524,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6062</v>
+        <v>6027</v>
       </c>
       <c r="C7" t="n">
         <v>1040</v>
       </c>
       <c r="D7" t="n">
-        <v>3166</v>
+        <v>1599</v>
       </c>
       <c r="E7" t="n">
-        <v>953</v>
+        <v>666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2929603442975715</v>
+        <v>0.3375570197668525</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9163461538461538</v>
+        <v>0.6403846153846153</v>
       </c>
       <c r="H7" t="n">
-        <v>0.301010739102969</v>
+        <v>0.4165103189493433</v>
       </c>
     </row>
     <row r="8">
@@ -1552,25 +1552,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6062</v>
+        <v>6027</v>
       </c>
       <c r="C8" t="n">
         <v>88</v>
       </c>
       <c r="D8" t="n">
-        <v>4227</v>
+        <v>2638</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01720886374351721</v>
+        <v>0.01716417910447761</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8295454545454546</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01726993139342323</v>
+        <v>0.01743745261561789</v>
       </c>
     </row>
   </sheetData>
@@ -1676,49 +1676,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42357</v>
+        <v>42189</v>
       </c>
       <c r="C2" t="n">
-        <v>0.612124167017723</v>
+        <v>0.633441231716551</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5309903085752125</v>
+        <v>-0.4204002063058067</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.21644355026271</v>
+        <v>-0.1689938836248475</v>
       </c>
       <c r="F2" t="n">
-        <v>1.47997188423426</v>
+        <v>1.198076114563849</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01813701330704781</v>
+        <v>0.01508485229415462</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005453644025780862</v>
+        <v>0.002678423285690583</v>
       </c>
       <c r="I2" t="n">
-        <v>0.238402153126992</v>
+        <v>0.1504420583564436</v>
       </c>
       <c r="J2" t="n">
         <v>37</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6745961985927255</v>
+        <v>-0.5289626199235942</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4001143117696945</v>
+        <v>-0.3247552189011372</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5843986694932263</v>
+        <v>0.6028445716683406</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6555827461562668</v>
+        <v>0.6751325590064264</v>
       </c>
       <c r="O2" t="n">
-        <v>0.007512158054433928</v>
+        <v>0.00509283627725927</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03233080894348263</v>
+        <v>0.02824090555964559</v>
       </c>
     </row>
     <row r="3">
@@ -1728,25 +1728,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42357</v>
+        <v>42189</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6387348515156402</v>
+        <v>0.6666621671391194</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4248389224536601</v>
+        <v>0.3328607611223207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4257580124026736</v>
+        <v>0.3365875295407754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8012406998467084</v>
+        <v>0.6654432392193128</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005453644025780862</v>
+        <v>0.002678423285690583</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1755,16 +1755,16 @@
         <v>37</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3935112588446121</v>
+        <v>0.3041982594555411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4582346705762154</v>
+        <v>0.3615703292602294</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5993290038584366</v>
+        <v>0.6263042332286862</v>
       </c>
       <c r="N3" t="n">
-        <v>0.675517385188084</v>
+        <v>0.7010101900319567</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
